--- a/artfynd/A 23503-2026 artfynd.xlsx
+++ b/artfynd/A 23503-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1229,6 +1229,342 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134194391</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488685</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6666403</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134195368</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488664</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6666468</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Betade tqllar</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134193323</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488783</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6666390</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23503-2026 artfynd.xlsx
+++ b/artfynd/A 23503-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1231,53 +1231,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134194391</v>
+        <v>134195368</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gettjärnsbäcken, Dlr</t>
+          <t>Gettjärnsbäcken, Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488685</v>
+        <v>488664</v>
       </c>
       <c r="R7" t="n">
-        <v>6666403</v>
+        <v>6666468</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,7 +1301,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,14 +1311,19 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Betade tqllar</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1331,60 +1331,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134195368</v>
+        <v>134194391</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gettjärnsbäcken, Gettjärnsbäcken, Dlr</t>
+          <t>Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488664</v>
+        <v>488685</v>
       </c>
       <c r="R8" t="n">
-        <v>6666468</v>
+        <v>6666403</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,19 +1428,14 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Betade tqllar</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1443,12 +1443,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1565,6 +1565,113 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134226109</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>488682</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6666521</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23503-2026 artfynd.xlsx
+++ b/artfynd/A 23503-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,6 +1672,863 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134268312</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västerdalarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488736</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6666428</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134268311</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91978</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västerdalarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>488735</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6666425</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Låga, rikligt.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134268565</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>488742</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6666450</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134268313</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Västerdalarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>488718</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6666442</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Betad tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134268309</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västerdalarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>488777</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6666411</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134268310</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västerdalarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>488738</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6666439</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134268364</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>488674</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6666508</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134268497</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>488716</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6666426</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosöksspår tretå? Långt ned på klen äldre undertryckt gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23503-2026 artfynd.xlsx
+++ b/artfynd/A 23503-2026 artfynd.xlsx
@@ -1789,7 +1789,7 @@
         <v>134268311</v>
       </c>
       <c r="B12" t="n">
-        <v>91978</v>
+        <v>91979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2108,53 +2108,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134268309</v>
+        <v>134268310</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>99097</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerdalarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488777</v>
+        <v>488738</v>
       </c>
       <c r="R15" t="n">
-        <v>6666411</v>
+        <v>6666439</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,7 +2188,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2220,48 +2215,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134268310</v>
+        <v>134268309</v>
       </c>
       <c r="B16" t="n">
-        <v>99096</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerdalarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488738</v>
+        <v>488777</v>
       </c>
       <c r="R16" t="n">
-        <v>6666439</v>
+        <v>6666411</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 23503-2026 artfynd.xlsx
+++ b/artfynd/A 23503-2026 artfynd.xlsx
@@ -1996,10 +1996,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134268313</v>
+        <v>134268310</v>
       </c>
       <c r="B14" t="n">
-        <v>57162</v>
+        <v>99098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488718</v>
+        <v>488738</v>
       </c>
       <c r="R14" t="n">
-        <v>6666442</v>
+        <v>6666439</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2076,12 +2076,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Betad tall</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,48 +2103,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134268310</v>
+        <v>134268309</v>
       </c>
       <c r="B15" t="n">
-        <v>99098</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerdalarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488738</v>
+        <v>488777</v>
       </c>
       <c r="R15" t="n">
-        <v>6666439</v>
+        <v>6666411</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,53 +2215,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134268309</v>
+        <v>134268313</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>57162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerdalarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488777</v>
+        <v>488718</v>
       </c>
       <c r="R16" t="n">
-        <v>6666411</v>
+        <v>6666442</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2290,7 +2285,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2300,7 +2295,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Betad tall</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 23503-2026 artfynd.xlsx
+++ b/artfynd/A 23503-2026 artfynd.xlsx
@@ -1789,7 +1789,7 @@
         <v>134268311</v>
       </c>
       <c r="B12" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134268310</v>
+        <v>134268313</v>
       </c>
       <c r="B14" t="n">
-        <v>99098</v>
+        <v>57162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488738</v>
+        <v>488718</v>
       </c>
       <c r="R14" t="n">
-        <v>6666439</v>
+        <v>6666442</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2076,7 +2076,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Betad tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,53 +2108,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134268309</v>
+        <v>134268310</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>99105</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerdalarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488777</v>
+        <v>488738</v>
       </c>
       <c r="R15" t="n">
-        <v>6666411</v>
+        <v>6666439</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,48 +2215,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134268313</v>
+        <v>134268309</v>
       </c>
       <c r="B16" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerdalarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488718</v>
+        <v>488777</v>
       </c>
       <c r="R16" t="n">
-        <v>6666442</v>
+        <v>6666411</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2285,7 +2290,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2295,12 +2300,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Betad tall</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 23503-2026 artfynd.xlsx
+++ b/artfynd/A 23503-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,30 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131430513</v>
+        <v>134197900</v>
       </c>
       <c r="B2" t="n">
-        <v>91866</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488813</v>
+        <v>488656</v>
       </c>
       <c r="R2" t="n">
-        <v>6666605</v>
+        <v>6666392</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -736,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131430053</v>
+        <v>134193323</v>
       </c>
       <c r="B3" t="n">
-        <v>57100</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,32 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -823,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488765</v>
+        <v>488783</v>
       </c>
       <c r="R3" t="n">
-        <v>6666432</v>
+        <v>6666390</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,22 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131430555</v>
+        <v>134268309</v>
       </c>
       <c r="B4" t="n">
-        <v>57100</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,42 +905,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gettjärnsbäcken, Dlr</t>
+          <t>Västerdalarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488713</v>
+        <v>488777</v>
       </c>
       <c r="R4" t="n">
-        <v>6666563</v>
+        <v>6666411</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,22 +964,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,22 +994,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131430111</v>
+        <v>134268312</v>
       </c>
       <c r="B5" t="n">
-        <v>57100</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,42 +1017,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gettjärnsbäcken, Dlr</t>
+          <t>Västerdalarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488717</v>
+        <v>488736</v>
       </c>
       <c r="R5" t="n">
-        <v>6666459</v>
+        <v>6666428</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,22 +1076,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,22 +1106,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131430353</v>
+        <v>134268364</v>
       </c>
       <c r="B6" t="n">
-        <v>57100</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,27 +1129,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1159,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488744</v>
+        <v>488674</v>
       </c>
       <c r="R6" t="n">
-        <v>6666601</v>
+        <v>6666508</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,22 +1188,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,27 +1220,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134194391</v>
+        <v>134268565</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1262,7 +1251,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1271,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488685</v>
+        <v>488742</v>
       </c>
       <c r="R7" t="n">
-        <v>6666403</v>
+        <v>6666450</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1301,29 +1290,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1343,48 +1322,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134195368</v>
+        <v>134194391</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gettjärnsbäcken, Gettjärnsbäcken, Dlr</t>
+          <t>Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488664</v>
+        <v>488685</v>
       </c>
       <c r="R8" t="n">
-        <v>6666468</v>
+        <v>6666403</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,19 +1407,14 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Betade tqllar</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1443,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134193323</v>
+        <v>134268497</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,16 +1445,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1484,21 +1463,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488783</v>
+        <v>488716</v>
       </c>
       <c r="R9" t="n">
-        <v>6666390</v>
+        <v>6666426</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1525,29 +1499,24 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosöksspår tretå? Långt ned på klen äldre undertryckt gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1567,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134226109</v>
+        <v>131430053</v>
       </c>
       <c r="B10" t="n">
-        <v>8460</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,46 +1547,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488682</v>
+        <v>488765</v>
       </c>
       <c r="R10" t="n">
-        <v>6666521</v>
+        <v>6666432</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,12 +1611,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,72 +1635,71 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134268312</v>
+        <v>131430111</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västerdalarna, Dlr</t>
+          <t>Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488736</v>
+        <v>488717</v>
       </c>
       <c r="R11" t="n">
-        <v>6666428</v>
+        <v>6666459</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,22 +1723,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,56 +1753,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134268311</v>
+        <v>131430353</v>
       </c>
       <c r="B12" t="n">
-        <v>91987</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västerdalarna, Dlr</t>
+          <t>Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488735</v>
+        <v>488744</v>
       </c>
       <c r="R12" t="n">
-        <v>6666425</v>
+        <v>6666601</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1847,27 +1835,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Låga, rikligt.</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,50 +1865,50 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134268565</v>
+        <v>131430555</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1934,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488742</v>
+        <v>488713</v>
       </c>
       <c r="R13" t="n">
-        <v>6666450</v>
+        <v>6666563</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1964,12 +1947,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134268313</v>
+        <v>134195368</v>
       </c>
       <c r="B14" t="n">
         <v>57162</v>
@@ -2027,17 +2020,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västerdalarna, Dlr</t>
+          <t>Gettjärnsbäcken, Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488718</v>
+        <v>488664</v>
       </c>
       <c r="R14" t="n">
-        <v>6666442</v>
+        <v>6666468</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2076,12 +2069,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Betad tall</t>
+          <t>Betade tqllar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,10 +2101,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134268310</v>
+        <v>134268313</v>
       </c>
       <c r="B15" t="n">
-        <v>99105</v>
+        <v>57162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2119,21 +2112,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2143,13 +2136,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488738</v>
+        <v>488718</v>
       </c>
       <c r="R15" t="n">
-        <v>6666439</v>
+        <v>6666442</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2178,7 +2171,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2188,7 +2181,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Betad tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,53 +2213,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134268309</v>
+        <v>134226109</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västerdalarna, Dlr</t>
+          <t>Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488777</v>
+        <v>488682</v>
       </c>
       <c r="R16" t="n">
-        <v>6666411</v>
+        <v>6666521</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,92 +2290,78 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134268364</v>
+        <v>134268310</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>99112</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gettjärnsbäcken, Dlr</t>
+          <t>Västerdalarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488674</v>
+        <v>488738</v>
       </c>
       <c r="R17" t="n">
-        <v>6666508</v>
+        <v>6666439</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2397,12 +2385,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,44 +2415,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134268497</v>
+        <v>134197238</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>99099</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2464,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488716</v>
+        <v>488656</v>
       </c>
       <c r="R18" t="n">
-        <v>6666426</v>
+        <v>6666392</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2494,24 +2492,34 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Födosöksspår tretå? Långt ned på klen äldre undertryckt gran</t>
+          <t>Ca 50 st blommande ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2528,6 +2536,103 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134268460</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>488716</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6666426</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23503-2026 artfynd.xlsx
+++ b/artfynd/A 23503-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2213,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134226109</v>
+        <v>134605964</v>
       </c>
       <c r="B16" t="n">
-        <v>8460</v>
+        <v>57153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,46 +2224,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488682</v>
+        <v>488793</v>
       </c>
       <c r="R16" t="n">
-        <v>6666521</v>
+        <v>6666646</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2287,12 +2283,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,29 +2307,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134268310</v>
+        <v>134226109</v>
       </c>
       <c r="B17" t="n">
-        <v>99112</v>
+        <v>8460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,37 +2336,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västerdalarna, Dlr</t>
+          <t>Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488738</v>
+        <v>488682</v>
       </c>
       <c r="R17" t="n">
-        <v>6666439</v>
+        <v>6666521</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2388,49 +2402,40 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134197238</v>
+        <v>134268310</v>
       </c>
       <c r="B18" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,37 +2443,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gettjärnsbäcken, Dlr</t>
+          <t>Västerdalarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488656</v>
+        <v>488738</v>
       </c>
       <c r="R18" t="n">
-        <v>6666392</v>
+        <v>6666439</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2497,7 +2502,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,12 +2512,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 50 st blommande ex</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,22 +2527,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134268460</v>
+        <v>134197238</v>
       </c>
       <c r="B19" t="n">
-        <v>99001</v>
+        <v>99099</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223049</v>
+        <v>220093</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488716</v>
+        <v>488656</v>
       </c>
       <c r="R19" t="n">
-        <v>6666426</v>
+        <v>6666392</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2604,12 +2604,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ca 50 st blommande ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,6 +2648,103 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134268460</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>488716</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6666426</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23503-2026 artfynd.xlsx
+++ b/artfynd/A 23503-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2651,10 +2651,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134268460</v>
+        <v>134615212</v>
       </c>
       <c r="B20" t="n">
-        <v>99001</v>
+        <v>99099</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,21 +2662,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223049</v>
+        <v>220093</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488716</v>
+        <v>488846</v>
       </c>
       <c r="R20" t="n">
-        <v>6666426</v>
+        <v>6666661</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2716,12 +2716,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,15 +2736,112 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134268460</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>488716</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6666426</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Tobias Hellberg</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Tobias Hellberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
